--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0103C903-9CA8-4938-9853-D3FC3534B62C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F743DC30-A8CE-4209-A12C-E15E9369AE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="83">
   <si>
     <t>Part Number</t>
   </si>
@@ -278,6 +278,12 @@
   </si>
   <si>
     <t>SMC</t>
+  </si>
+  <si>
+    <t>ESD9L5.0ST5G</t>
+  </si>
+  <si>
+    <t>ESD9L5.0ST5G SOD-923</t>
   </si>
 </sst>
 </file>
@@ -713,8 +719,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="16.140625" customWidth="1"/>
+    <col min="3" max="3" width="36.140625" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
+    <col min="5" max="5" width="24.42578125" customWidth="1"/>
+    <col min="6" max="6" width="19" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1130,6 +1144,29 @@
         <v>13</v>
       </c>
     </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>81</v>
+      </c>
+      <c r="B19" t="s">
+        <v>72</v>
+      </c>
+      <c r="C19" t="s">
+        <v>82</v>
+      </c>
+      <c r="D19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+      <c r="F19" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F743DC30-A8CE-4209-A12C-E15E9369AE7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9D5A2F-7CC6-4E42-9363-3F08C98DDC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="88">
   <si>
     <t>Part Number</t>
   </si>
@@ -284,6 +284,21 @@
   </si>
   <si>
     <t>ESD9L5.0ST5G SOD-923</t>
+  </si>
+  <si>
+    <t>1N5819W</t>
+  </si>
+  <si>
+    <t>BAT54A</t>
+  </si>
+  <si>
+    <t>BAT54A SOT23</t>
+  </si>
+  <si>
+    <t>Diode Array 1C2C3A</t>
+  </si>
+  <si>
+    <t>NXP</t>
   </si>
 </sst>
 </file>
@@ -660,8 +675,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.28515625" customWidth="1"/>
+    <col min="2" max="2" width="11.28515625" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" customWidth="1"/>
+    <col min="5" max="5" width="20.28515625" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="21.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -710,6 +734,29 @@
       </c>
       <c r="G2" s="3" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -719,7 +766,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -1167,6 +1214,29 @@
         <v>13</v>
       </c>
     </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>83</v>
+      </c>
+      <c r="D20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB9D5A2F-7CC6-4E42-9363-3F08C98DDC2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DF72A5-19C0-41B6-9A3F-B8576363916E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="91">
   <si>
     <t>Part Number</t>
   </si>
@@ -299,6 +299,15 @@
   </si>
   <si>
     <t>NXP</t>
+  </si>
+  <si>
+    <t>LED: 3MM_G</t>
+  </si>
+  <si>
+    <t>GNL-3014UBD-TL</t>
+  </si>
+  <si>
+    <t>G-nor Electronics</t>
   </si>
 </sst>
 </file>
@@ -766,7 +775,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -775,6 +784,7 @@
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="24.42578125" customWidth="1"/>
     <col min="6" max="6" width="19" customWidth="1"/>
+    <col min="7" max="7" width="24.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -1237,6 +1247,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" t="s">
+        <v>89</v>
+      </c>
+      <c r="D21" t="s">
+        <v>89</v>
+      </c>
+      <c r="E21" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6DF72A5-19C0-41B6-9A3F-B8576363916E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0580C7D9-6B18-4B33-BAC9-44BF07232A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="97">
   <si>
     <t>Part Number</t>
   </si>
@@ -308,6 +308,24 @@
   </si>
   <si>
     <t>G-nor Electronics</t>
+  </si>
+  <si>
+    <t>Rohm</t>
+  </si>
+  <si>
+    <t>UDZSTE-175.6B</t>
+  </si>
+  <si>
+    <t>UDZSTE-175.6B SOD323</t>
+  </si>
+  <si>
+    <t>Schottky 3C1A</t>
+  </si>
+  <si>
+    <t>MMBZ5222BLG</t>
+  </si>
+  <si>
+    <t>MMBZ5222BLG SOT23</t>
   </si>
 </sst>
 </file>
@@ -775,7 +793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -1270,7 +1288,77 @@
         <v>90</v>
       </c>
     </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B22" t="s">
+        <v>32</v>
+      </c>
+      <c r="C22" t="s">
+        <v>93</v>
+      </c>
+      <c r="D22" t="s">
+        <v>92</v>
+      </c>
+      <c r="E22" t="s">
+        <v>17</v>
+      </c>
+      <c r="F22" t="s">
+        <v>32</v>
+      </c>
+      <c r="G22" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
+        <v>32</v>
+      </c>
+      <c r="C23" t="s">
+        <v>93</v>
+      </c>
+      <c r="D23" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s">
+        <v>32</v>
+      </c>
+      <c r="G23" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>95</v>
+      </c>
+      <c r="B24" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>95</v>
+      </c>
+      <c r="E24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0580C7D9-6B18-4B33-BAC9-44BF07232A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C958C1-ACB9-4190-A075-3B4F5C060285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="103">
   <si>
     <t>Part Number</t>
   </si>
@@ -326,6 +326,24 @@
   </si>
   <si>
     <t>MMBZ5222BLG SOT23</t>
+  </si>
+  <si>
+    <t>SS3P6L-M3/86A</t>
+  </si>
+  <si>
+    <t>Schottky_SS3P6L</t>
+  </si>
+  <si>
+    <t>SS3P6L</t>
+  </si>
+  <si>
+    <t>SMPC</t>
+  </si>
+  <si>
+    <t>PMEG6010CEJ</t>
+  </si>
+  <si>
+    <t>PMEG6010CEJ SOD323</t>
   </si>
 </sst>
 </file>
@@ -793,7 +811,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -1357,6 +1375,52 @@
         <v>13</v>
       </c>
     </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>97</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
+        <v>97</v>
+      </c>
+      <c r="E25" t="s">
+        <v>98</v>
+      </c>
+      <c r="F25" t="s">
+        <v>100</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>101</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D26" t="s">
+        <v>101</v>
+      </c>
+      <c r="E26" t="s">
+        <v>17</v>
+      </c>
+      <c r="F26" t="s">
+        <v>32</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C958C1-ACB9-4190-A075-3B4F5C060285}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E58049-4E05-43E5-9356-17A89F79CE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="23085" windowHeight="13635" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="111">
   <si>
     <t>Part Number</t>
   </si>
@@ -344,6 +344,30 @@
   </si>
   <si>
     <t>PMEG6010CEJ SOD323</t>
+  </si>
+  <si>
+    <t>2Д663АС9</t>
+  </si>
+  <si>
+    <t>2Д663АС9 КТ89</t>
+  </si>
+  <si>
+    <t>TO-252-2</t>
+  </si>
+  <si>
+    <t>Schottky Array 1A2C3A</t>
+  </si>
+  <si>
+    <t>АЕЯР.432120.223 ТУ</t>
+  </si>
+  <si>
+    <t>2Д706АС9</t>
+  </si>
+  <si>
+    <t>2Д706АС9 SOT23</t>
+  </si>
+  <si>
+    <t>aAO.339.582 ТУ</t>
   </si>
 </sst>
 </file>
@@ -720,7 +744,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -802,6 +826,52 @@
       </c>
       <c r="G3" s="3" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D4" t="s">
+        <v>103</v>
+      </c>
+      <c r="E4" t="s">
+        <v>106</v>
+      </c>
+      <c r="F4" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>108</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>109</v>
+      </c>
+      <c r="D5" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2E58049-4E05-43E5-9356-17A89F79CE7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C99072-A644-4B2D-9E39-5FC17BC1299F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="23085" windowHeight="13635" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="114">
   <si>
     <t>Part Number</t>
   </si>
@@ -368,6 +368,15 @@
   </si>
   <si>
     <t>aAO.339.582 ТУ</t>
+  </si>
+  <si>
+    <t>2C117Б</t>
+  </si>
+  <si>
+    <t>Diode Zener</t>
+  </si>
+  <si>
+    <t>аА0.339.736ТУ</t>
   </si>
 </sst>
 </file>
@@ -424,11 +433,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -881,7 +891,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -1261,7 +1271,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -1284,7 +1294,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>77</v>
       </c>
@@ -1307,7 +1317,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>81</v>
       </c>
@@ -1330,7 +1340,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>83</v>
       </c>
@@ -1353,7 +1363,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>89</v>
       </c>
@@ -1376,7 +1386,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -1399,7 +1409,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>92</v>
       </c>
@@ -1422,7 +1432,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>95</v>
       </c>
@@ -1445,7 +1455,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>97</v>
       </c>
@@ -1468,7 +1478,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>101</v>
       </c>
@@ -1489,6 +1499,26 @@
       </c>
       <c r="G26" s="3" t="s">
         <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>111</v>
+      </c>
+      <c r="C27" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" t="s">
+        <v>111</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>113</v>
       </c>
     </row>
   </sheetData>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C99072-A644-4B2D-9E39-5FC17BC1299F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A50066-EBF2-4280-B324-DF3BA9362278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="1425" yWindow="1425" windowWidth="23085" windowHeight="13635" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="118">
   <si>
     <t>Part Number</t>
   </si>
@@ -377,6 +377,18 @@
   </si>
   <si>
     <t>аА0.339.736ТУ</t>
+  </si>
+  <si>
+    <t>2Д707АС9</t>
+  </si>
+  <si>
+    <t>2Д707АС9 SOT23</t>
+  </si>
+  <si>
+    <t>Diode Array 1A2CA3A</t>
+  </si>
+  <si>
+    <t>аА0.339.583ТУ</t>
   </si>
 </sst>
 </file>
@@ -754,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" customWidth="1"/>
@@ -882,6 +894,29 @@
       </c>
       <c r="H5" t="s">
         <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" t="s">
+        <v>116</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>
@@ -1517,7 +1552,7 @@
       <c r="F27" t="s">
         <v>111</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" t="s">
         <v>113</v>
       </c>
     </row>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97A50066-EBF2-4280-B324-DF3BA9362278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187C824A-4370-4266-AEE4-975EF662CBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1425" yWindow="1425" windowWidth="23085" windowHeight="13635" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="119">
   <si>
     <t>Part Number</t>
   </si>
@@ -389,6 +389,9 @@
   </si>
   <si>
     <t>аА0.339.583ТУ</t>
+  </si>
+  <si>
+    <t>SOD123W</t>
   </si>
 </sst>
 </file>
@@ -445,12 +448,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -915,7 +917,7 @@
       <c r="F6" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" t="s">
         <v>117</v>
       </c>
     </row>
@@ -926,7 +928,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -1556,6 +1558,26 @@
         <v>113</v>
       </c>
     </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D28" t="s">
+        <v>50</v>
+      </c>
+      <c r="E28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F28" t="s">
+        <v>118</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{187C824A-4370-4266-AEE4-975EF662CBB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAFBBBA-74F3-4909-8681-7B156A4E687E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="117">
   <si>
     <t>Part Number</t>
   </si>
@@ -190,15 +190,6 @@
     <t>ES07D-GS18</t>
   </si>
   <si>
-    <t>DO-219AB</t>
-  </si>
-  <si>
-    <t>ES07D-GS18 DO-219AB</t>
-  </si>
-  <si>
-    <t>SMF</t>
-  </si>
-  <si>
     <t>1N4148WS</t>
   </si>
   <si>
@@ -392,6 +383,9 @@
   </si>
   <si>
     <t>SOD123W</t>
+  </si>
+  <si>
+    <t>ES07D-GS18 SOD123W</t>
   </si>
 </sst>
 </file>
@@ -831,94 +825,94 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
         <v>12</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" t="s">
         <v>103</v>
       </c>
-      <c r="B4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4" t="s">
         <v>104</v>
-      </c>
-      <c r="D4" t="s">
-        <v>103</v>
-      </c>
-      <c r="E4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F4" t="s">
-        <v>105</v>
-      </c>
-      <c r="H4" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D5" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="E5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1148,40 +1142,21 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C10" t="s">
-        <v>52</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>49</v>
-      </c>
+      <c r="A10" s="2"/>
+      <c r="G10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E11" t="s">
         <v>45</v>
@@ -1195,16 +1170,16 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
         <v>45</v>
@@ -1218,91 +1193,91 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D13" t="s">
         <v>58</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="E13" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C13" t="s">
+      <c r="F13" t="s">
         <v>60</v>
       </c>
-      <c r="D13" t="s">
+      <c r="G13" t="s">
         <v>61</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" t="s">
-        <v>67</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>66</v>
+      </c>
+      <c r="D15" t="s">
+        <v>67</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C15" t="s">
-        <v>69</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>13</v>
@@ -1310,16 +1285,16 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D17" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
@@ -1333,22 +1308,22 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>13</v>
@@ -1356,22 +1331,22 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C19" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>13</v>
@@ -1379,16 +1354,16 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B20" t="s">
         <v>18</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E20" t="s">
         <v>17</v>
@@ -1402,39 +1377,39 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D22" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -1443,21 +1418,21 @@
         <v>32</v>
       </c>
       <c r="G22" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B23" t="s">
         <v>32</v>
       </c>
       <c r="C23" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E23" t="s">
         <v>17</v>
@@ -1466,24 +1441,24 @@
         <v>32</v>
       </c>
       <c r="G23" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B24" t="s">
         <v>12</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F24" t="s">
         <v>12</v>
@@ -1494,22 +1469,22 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>94</v>
+      </c>
+      <c r="B25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D25" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" t="s">
         <v>97</v>
-      </c>
-      <c r="B25" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" t="s">
-        <v>97</v>
-      </c>
-      <c r="E25" t="s">
-        <v>98</v>
-      </c>
-      <c r="F25" t="s">
-        <v>100</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>49</v>
@@ -1517,16 +1492,16 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
         <v>32</v>
       </c>
       <c r="C26" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E26" t="s">
         <v>17</v>
@@ -1540,30 +1515,33 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="E27" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="F27" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="H27" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>50</v>
       </c>
+      <c r="B28" t="s">
+        <v>115</v>
+      </c>
       <c r="C28" t="s">
-        <v>50</v>
+        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>50</v>
@@ -1572,7 +1550,7 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>49</v>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAFBBBA-74F3-4909-8681-7B156A4E687E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5408B0C-5C23-47B6-999B-18DDECFF11CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -346,9 +346,6 @@
     <t>TO-252-2</t>
   </si>
   <si>
-    <t>Schottky Array 1A2C3A</t>
-  </si>
-  <si>
     <t>АЕЯР.432120.223 ТУ</t>
   </si>
   <si>
@@ -386,6 +383,9 @@
   </si>
   <si>
     <t>ES07D-GS18 SOD123W</t>
+  </si>
+  <si>
+    <t>Diode Array 1A2C3A</t>
   </si>
 </sst>
 </file>
@@ -860,27 +860,27 @@
         <v>100</v>
       </c>
       <c r="E4" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="F4" t="s">
         <v>102</v>
       </c>
       <c r="H4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E5" t="s">
         <v>83</v>
@@ -889,30 +889,30 @@
         <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
       </c>
       <c r="C6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E6" t="s">
         <v>112</v>
-      </c>
-      <c r="D6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E6" t="s">
-        <v>113</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -1515,22 +1515,22 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>107</v>
+      </c>
+      <c r="C27" t="s">
+        <v>107</v>
+      </c>
+      <c r="D27" t="s">
+        <v>107</v>
+      </c>
+      <c r="E27" t="s">
         <v>108</v>
       </c>
-      <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>108</v>
-      </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
+        <v>107</v>
+      </c>
+      <c r="H27" t="s">
         <v>109</v>
-      </c>
-      <c r="F27" t="s">
-        <v>108</v>
-      </c>
-      <c r="H27" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -1538,10 +1538,10 @@
         <v>50</v>
       </c>
       <c r="B28" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" t="s">
         <v>115</v>
-      </c>
-      <c r="C28" t="s">
-        <v>116</v>
       </c>
       <c r="D28" t="s">
         <v>50</v>
@@ -1550,7 +1550,7 @@
         <v>45</v>
       </c>
       <c r="F28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>49</v>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5408B0C-5C23-47B6-999B-18DDECFF11CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867F0BE5-E55C-4E44-B3B2-F78D3D8CD03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="123">
   <si>
     <t>Part Number</t>
   </si>
@@ -386,6 +386,24 @@
   </si>
   <si>
     <t>Diode Array 1A2C3A</t>
+  </si>
+  <si>
+    <t>CASE 017AA</t>
+  </si>
+  <si>
+    <t>1N5349BRLG</t>
+  </si>
+  <si>
+    <t>1N5349BRLG CASE 017AA</t>
+  </si>
+  <si>
+    <t>1N5406</t>
+  </si>
+  <si>
+    <t>DO-201AD</t>
+  </si>
+  <si>
+    <t>1N5406 DO-201AD</t>
   </si>
 </sst>
 </file>
@@ -922,7 +940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -1556,6 +1574,52 @@
         <v>49</v>
       </c>
     </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>118</v>
+      </c>
+      <c r="B29" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" t="s">
+        <v>119</v>
+      </c>
+      <c r="D29" t="s">
+        <v>118</v>
+      </c>
+      <c r="E29" t="s">
+        <v>108</v>
+      </c>
+      <c r="F29" t="s">
+        <v>117</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>120</v>
+      </c>
+      <c r="B30" t="s">
+        <v>121</v>
+      </c>
+      <c r="C30" t="s">
+        <v>122</v>
+      </c>
+      <c r="D30" t="s">
+        <v>120</v>
+      </c>
+      <c r="E30" t="s">
+        <v>45</v>
+      </c>
+      <c r="F30" t="s">
+        <v>121</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867F0BE5-E55C-4E44-B3B2-F78D3D8CD03D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FFBCF3-2EE5-4801-94C7-37471AA0213D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="129">
   <si>
     <t>Part Number</t>
   </si>
@@ -404,13 +404,31 @@
   </si>
   <si>
     <t>1N5406 DO-201AD</t>
+  </si>
+  <si>
+    <t>GNL-3012GD</t>
+  </si>
+  <si>
+    <t>GNL-3012HD</t>
+  </si>
+  <si>
+    <t>GNL-3012YD</t>
+  </si>
+  <si>
+    <t>LED: 3MM_R</t>
+  </si>
+  <si>
+    <t>LED: 3MM_Y</t>
+  </si>
+  <si>
+    <t>GNL-3012</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -431,6 +449,13 @@
       <color indexed="8"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -940,7 +965,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.42578125" customWidth="1"/>
@@ -1620,7 +1645,77 @@
         <v>49</v>
       </c>
     </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>123</v>
+      </c>
+      <c r="B31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C31" t="s">
+        <v>123</v>
+      </c>
+      <c r="D31" t="s">
+        <v>123</v>
+      </c>
+      <c r="E31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" t="s">
+        <v>124</v>
+      </c>
+      <c r="D32" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" t="s">
+        <v>59</v>
+      </c>
+      <c r="F32" t="s">
+        <v>126</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>125</v>
+      </c>
+      <c r="B33" t="s">
+        <v>128</v>
+      </c>
+      <c r="C33" t="s">
+        <v>125</v>
+      </c>
+      <c r="D33" t="s">
+        <v>125</v>
+      </c>
+      <c r="E33" t="s">
+        <v>59</v>
+      </c>
+      <c r="F33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0FFBCF3-2EE5-4801-94C7-37471AA0213D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6E5CE2-989A-6E47-B96C-4FB497BCD715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="130">
   <si>
     <t>Part Number</t>
   </si>
@@ -151,9 +151,6 @@
     <t>SOD523</t>
   </si>
   <si>
-    <t>UMW (Youtai Semiconductor Co., Ltd.)</t>
-  </si>
-  <si>
     <t>BZV55-B3V3</t>
   </si>
   <si>
@@ -283,9 +280,6 @@
     <t>BAT54A</t>
   </si>
   <si>
-    <t>BAT54A SOT23</t>
-  </si>
-  <si>
     <t>Diode Array 1C2C3A</t>
   </si>
   <si>
@@ -352,9 +346,6 @@
     <t>2Д706АС9</t>
   </si>
   <si>
-    <t>2Д706АС9 SOT23</t>
-  </si>
-  <si>
     <t>aAO.339.582 ТУ</t>
   </si>
   <si>
@@ -370,9 +361,6 @@
     <t>2Д707АС9</t>
   </si>
   <si>
-    <t>2Д707АС9 SOT23</t>
-  </si>
-  <si>
     <t>Diode Array 1A2CA3A</t>
   </si>
   <si>
@@ -422,6 +410,21 @@
   </si>
   <si>
     <t>GNL-3012</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
+    <t>BAT54A SOT-23</t>
+  </si>
+  <si>
+    <t>2Д706АС9 SOT-23</t>
+  </si>
+  <si>
+    <t>2Д707АС9 SOT-23</t>
+  </si>
+  <si>
+    <t>1N5819W SOD123</t>
   </si>
 </sst>
 </file>
@@ -492,8 +495,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
-    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -509,9 +512,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -549,7 +552,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -655,7 +658,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -797,7 +800,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -806,18 +809,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.28515625" customWidth="1"/>
-    <col min="2" max="2" width="11.28515625" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="13.85546875" customWidth="1"/>
-    <col min="5" max="5" width="20.28515625" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="21.85546875" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -843,7 +842,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -866,96 +865,96 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" t="s">
+        <v>126</v>
+      </c>
+      <c r="D3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" t="s">
         <v>81</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
-      </c>
-      <c r="D3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E3" t="s">
-        <v>83</v>
       </c>
       <c r="F3" t="s">
         <v>12</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B4" t="s">
         <v>100</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
+        <v>99</v>
+      </c>
+      <c r="D4" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>102</v>
       </c>
-      <c r="C4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="B5" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D5" t="s">
         <v>102</v>
       </c>
-      <c r="H4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5" t="s">
-        <v>104</v>
-      </c>
       <c r="E5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F5" t="s">
         <v>12</v>
       </c>
       <c r="H5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F6" t="s">
         <v>12</v>
       </c>
       <c r="H6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -965,19 +964,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="36.140625" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="24.42578125" customWidth="1"/>
-    <col min="6" max="6" width="19" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" customWidth="1"/>
+    <col min="1" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="8" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1003,7 +998,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1026,7 +1021,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -1046,7 +1041,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -1069,7 +1064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -1092,7 +1087,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1112,347 +1107,366 @@
         <v>37</v>
       </c>
       <c r="G6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="B7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>40</v>
       </c>
-      <c r="C7" t="s">
-        <v>41</v>
-      </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G7" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
         <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>43</v>
       </c>
       <c r="B8" t="s">
         <v>35</v>
       </c>
       <c r="C8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
         <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" t="s">
-        <v>45</v>
       </c>
       <c r="F8" t="s">
         <v>37</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" t="s">
         <v>46</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>47</v>
       </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E9" t="s">
         <v>23</v>
       </c>
       <c r="F9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="s">
         <v>51</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
+        <v>53</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D11" t="s">
-        <v>51</v>
-      </c>
       <c r="E11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F11" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B12" t="s">
-        <v>30</v>
+      <c r="G11" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" t="s">
-        <v>45</v>
+        <v>56</v>
+      </c>
+      <c r="D12" t="s">
+        <v>57</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>58</v>
       </c>
       <c r="F12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="G12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" t="s">
         <v>59</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>60</v>
       </c>
-      <c r="G13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" t="s">
         <v>59</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>60</v>
       </c>
-      <c r="G14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
+      </c>
+      <c r="B15" t="s">
+        <v>68</v>
       </c>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
         <v>67</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>59</v>
+      <c r="E15" t="s">
+        <v>17</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
         <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" t="s">
-        <v>30</v>
+        <v>73</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C17" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" t="s">
         <v>73</v>
-      </c>
-      <c r="D17" t="s">
-        <v>72</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
       </c>
-      <c r="F17" t="s">
-        <v>32</v>
+      <c r="F17" s="2" t="s">
+        <v>76</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>74</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
       </c>
       <c r="C18" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E18" t="s">
         <v>17</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>77</v>
+      <c r="F18" t="s">
+        <v>70</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B19" t="s">
-        <v>69</v>
+        <v>18</v>
       </c>
       <c r="C19" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" t="s">
         <v>79</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
       </c>
       <c r="E19" t="s">
         <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>18</v>
+        <v>84</v>
       </c>
       <c r="C20" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D20" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E20" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" t="s">
+        <v>83</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" t="s">
         <v>17</v>
       </c>
-      <c r="F20" t="s">
-        <v>18</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="F21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G21" t="s">
         <v>86</v>
       </c>
-      <c r="B21" t="s">
-        <v>86</v>
-      </c>
-      <c r="C21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D21" t="s">
-        <v>86</v>
-      </c>
-      <c r="E21" t="s">
-        <v>59</v>
-      </c>
-      <c r="F21" t="s">
-        <v>85</v>
-      </c>
-      <c r="G21" s="3" t="s">
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>89</v>
       </c>
       <c r="B22" t="s">
         <v>32</v>
       </c>
       <c r="C22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
         <v>17</v>
@@ -1461,257 +1475,234 @@
         <v>32</v>
       </c>
       <c r="G22" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" t="s">
+        <v>91</v>
+      </c>
+      <c r="D23" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" t="s">
         <v>89</v>
       </c>
-      <c r="B23" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" t="s">
-        <v>89</v>
-      </c>
-      <c r="E23" t="s">
-        <v>17</v>
-      </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>92</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D24" t="s">
         <v>92</v>
       </c>
       <c r="E24" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" t="s">
         <v>96</v>
       </c>
-      <c r="C25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" t="s">
-        <v>94</v>
-      </c>
       <c r="E25" t="s">
-        <v>95</v>
+        <v>17</v>
       </c>
       <c r="F25" t="s">
-        <v>97</v>
-      </c>
-      <c r="G25" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E26" t="s">
+        <v>105</v>
+      </c>
+      <c r="F26" t="s">
+        <v>104</v>
+      </c>
+      <c r="H26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D26" t="s">
-        <v>98</v>
-      </c>
-      <c r="E26" t="s">
-        <v>17</v>
-      </c>
-      <c r="F26" t="s">
-        <v>32</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>107</v>
+      <c r="B27" t="s">
+        <v>110</v>
       </c>
       <c r="C27" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="D27" t="s">
-        <v>107</v>
+        <v>49</v>
       </c>
       <c r="E27" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="F27" t="s">
-        <v>107</v>
-      </c>
-      <c r="H27" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C28" t="s">
         <v>115</v>
       </c>
       <c r="D28" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>105</v>
       </c>
       <c r="F28" t="s">
-        <v>114</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B29" t="s">
         <v>117</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>44</v>
       </c>
       <c r="F29" t="s">
         <v>117</v>
       </c>
-      <c r="G29" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G29" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
+        <v>119</v>
+      </c>
+      <c r="B30" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" t="s">
+        <v>119</v>
+      </c>
+      <c r="D30" t="s">
+        <v>119</v>
+      </c>
+      <c r="E30" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" t="s">
+        <v>83</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>120</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C31" t="s">
+        <v>120</v>
+      </c>
+      <c r="D31" t="s">
+        <v>120</v>
+      </c>
+      <c r="E31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" t="s">
+        <v>122</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
         <v>121</v>
       </c>
-      <c r="C30" t="s">
-        <v>122</v>
-      </c>
-      <c r="D30" t="s">
-        <v>120</v>
-      </c>
-      <c r="E30" t="s">
-        <v>45</v>
-      </c>
-      <c r="F30" t="s">
+      <c r="B32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" t="s">
         <v>121</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="D32" t="s">
+        <v>121</v>
+      </c>
+      <c r="E32" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" t="s">
         <v>123</v>
       </c>
-      <c r="B31" t="s">
-        <v>128</v>
-      </c>
-      <c r="C31" t="s">
-        <v>123</v>
-      </c>
-      <c r="D31" t="s">
-        <v>123</v>
-      </c>
-      <c r="E31" t="s">
-        <v>59</v>
-      </c>
-      <c r="F31" t="s">
+      <c r="G32" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>124</v>
-      </c>
-      <c r="B32" t="s">
-        <v>128</v>
-      </c>
-      <c r="C32" t="s">
-        <v>124</v>
-      </c>
-      <c r="D32" t="s">
-        <v>124</v>
-      </c>
-      <c r="E32" t="s">
-        <v>59</v>
-      </c>
-      <c r="F32" t="s">
-        <v>126</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>125</v>
-      </c>
-      <c r="B33" t="s">
-        <v>128</v>
-      </c>
-      <c r="C33" t="s">
-        <v>125</v>
-      </c>
-      <c r="D33" t="s">
-        <v>125</v>
-      </c>
-      <c r="E33" t="s">
-        <v>59</v>
-      </c>
-      <c r="F33" t="s">
-        <v>127</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garou/Documents/work/elem_altium_db2/library/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6E5CE2-989A-6E47-B96C-4FB497BCD715}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8188B33-192D-4978-8229-4649054B284B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="132">
   <si>
     <t>Part Number</t>
   </si>
@@ -425,6 +425,12 @@
   </si>
   <si>
     <t>1N5819W SOD123</t>
+  </si>
+  <si>
+    <t>BZV55-C20V0</t>
+  </si>
+  <si>
+    <t>BZV55-C20V0 SOD80C</t>
   </si>
 </sst>
 </file>
@@ -495,8 +501,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -512,9 +518,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office 2013–2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -552,7 +558,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -658,7 +664,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -800,7 +806,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -809,14 +815,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -842,7 +848,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -865,7 +871,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -888,7 +894,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -911,7 +917,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -934,7 +940,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>107</v>
       </c>
@@ -964,15 +970,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="25.83203125" customWidth="1"/>
-    <col min="4" max="8" width="20.83203125" customWidth="1"/>
+    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -998,7 +1004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1021,7 +1027,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -1041,7 +1047,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -1064,7 +1070,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -1087,7 +1093,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1110,7 +1116,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1124,7 +1130,7 @@
         <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>105</v>
       </c>
       <c r="F7" t="s">
         <v>39</v>
@@ -1133,7 +1139,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1156,7 +1162,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
@@ -1179,7 +1185,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -1202,7 +1208,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>52</v>
       </c>
@@ -1225,7 +1231,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -1248,7 +1254,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -1271,7 +1277,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>64</v>
       </c>
@@ -1294,7 +1300,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -1317,7 +1323,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1340,7 +1346,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>73</v>
       </c>
@@ -1363,7 +1369,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>77</v>
       </c>
@@ -1386,7 +1392,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>79</v>
       </c>
@@ -1409,7 +1415,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -1432,7 +1438,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>87</v>
       </c>
@@ -1455,7 +1461,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>87</v>
       </c>
@@ -1478,7 +1484,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -1501,7 +1507,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>92</v>
       </c>
@@ -1524,7 +1530,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -1547,7 +1553,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -1567,7 +1573,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -1590,7 +1596,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>114</v>
       </c>
@@ -1613,7 +1619,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>116</v>
       </c>
@@ -1636,7 +1642,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>119</v>
       </c>
@@ -1659,7 +1665,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>120</v>
       </c>
@@ -1678,11 +1684,11 @@
       <c r="F31" t="s">
         <v>122</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="G31" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>121</v>
       </c>
@@ -1701,8 +1707,31 @@
       <c r="F32" t="s">
         <v>123</v>
       </c>
-      <c r="G32" s="3" t="s">
+      <c r="G32" t="s">
         <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>130</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
+        <v>131</v>
+      </c>
+      <c r="D33" t="s">
+        <v>130</v>
+      </c>
+      <c r="E33" t="s">
+        <v>105</v>
+      </c>
+      <c r="F33" t="s">
+        <v>39</v>
+      </c>
+      <c r="G33" t="s">
+        <v>41</v>
       </c>
     </row>
   </sheetData>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8188B33-192D-4978-8229-4649054B284B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BD35AA4-C646-4C94-B5AD-E1680ECA621E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="30240" yWindow="1440" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="143">
   <si>
     <t>Part Number</t>
   </si>
@@ -431,13 +431,46 @@
   </si>
   <si>
     <t>BZV55-C20V0 SOD80C</t>
+  </si>
+  <si>
+    <t>BAW56W</t>
+  </si>
+  <si>
+    <t>BAW56W SOT23</t>
+  </si>
+  <si>
+    <t>BAV99</t>
+  </si>
+  <si>
+    <t>BAV99 SOT23</t>
+  </si>
+  <si>
+    <t>BZV55-C6V2</t>
+  </si>
+  <si>
+    <t>BZV55-C6V8</t>
+  </si>
+  <si>
+    <t>BZV55-C6V2 SOD80C</t>
+  </si>
+  <si>
+    <t>BZV55-C6V8 SOD80C</t>
+  </si>
+  <si>
+    <t>RS3M</t>
+  </si>
+  <si>
+    <t>RS3M SMC</t>
+  </si>
+  <si>
+    <t>DIODES</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,6 +498,12 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Inter"/>
     </font>
   </fonts>
   <fills count="3">
@@ -494,11 +533,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Accent 3 2" xfId="1" xr:uid="{07D6D35A-A25D-4183-ACA2-756DA14CBAEA}"/>
@@ -814,15 +855,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67671D6E-5D55-4C0C-9FE7-A86F937C6875}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
     <col min="3" max="3" width="25.85546875" customWidth="1"/>
     <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -848,7 +889,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -871,7 +912,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
         <v>80</v>
       </c>
@@ -894,7 +935,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>98</v>
       </c>
@@ -917,7 +958,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
         <v>102</v>
       </c>
@@ -940,7 +981,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>107</v>
       </c>
@@ -963,22 +1004,69 @@
         <v>109</v>
       </c>
     </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E8" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H40"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="20.85546875" customWidth="1"/>
     <col min="3" max="3" width="25.85546875" customWidth="1"/>
     <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1004,7 +1092,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="2" t="s">
         <v>14</v>
       </c>
@@ -1027,7 +1115,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>20</v>
       </c>
@@ -1047,7 +1135,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -1070,7 +1158,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>29</v>
       </c>
@@ -1093,7 +1181,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1116,7 +1204,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
         <v>38</v>
       </c>
@@ -1139,7 +1227,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1162,7 +1250,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8">
       <c r="A9" s="2" t="s">
         <v>45</v>
       </c>
@@ -1185,7 +1273,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -1208,7 +1296,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="2" t="s">
         <v>52</v>
       </c>
@@ -1231,7 +1319,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -1254,7 +1342,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -1277,7 +1365,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" t="s">
         <v>64</v>
       </c>
@@ -1300,7 +1388,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -1323,7 +1411,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" t="s">
         <v>71</v>
       </c>
@@ -1346,7 +1434,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" t="s">
         <v>73</v>
       </c>
@@ -1369,7 +1457,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="A18" t="s">
         <v>77</v>
       </c>
@@ -1392,7 +1480,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8">
       <c r="A19" t="s">
         <v>79</v>
       </c>
@@ -1415,7 +1503,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -1438,7 +1526,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
         <v>87</v>
       </c>
@@ -1461,7 +1549,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8">
       <c r="A22" t="s">
         <v>87</v>
       </c>
@@ -1484,7 +1572,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8">
       <c r="A23" t="s">
         <v>90</v>
       </c>
@@ -1507,7 +1595,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8">
       <c r="A24" t="s">
         <v>92</v>
       </c>
@@ -1530,7 +1618,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -1553,7 +1641,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
         <v>104</v>
       </c>
@@ -1573,7 +1661,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8">
       <c r="A27" t="s">
         <v>49</v>
       </c>
@@ -1592,11 +1680,11 @@
       <c r="F27" t="s">
         <v>110</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="G27" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8">
       <c r="A28" t="s">
         <v>114</v>
       </c>
@@ -1619,7 +1707,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8">
       <c r="A29" t="s">
         <v>116</v>
       </c>
@@ -1638,11 +1726,11 @@
       <c r="F29" t="s">
         <v>117</v>
       </c>
-      <c r="G29" s="2" t="s">
+      <c r="G29" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8">
       <c r="A30" t="s">
         <v>119</v>
       </c>
@@ -1661,78 +1749,193 @@
       <c r="F30" t="s">
         <v>83</v>
       </c>
-      <c r="G30" s="3" t="s">
+      <c r="G30" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+    <row r="31" spans="1:8">
+      <c r="A31" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B31" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D31" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="E31" t="s">
+      <c r="E31" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F31" t="s">
+      <c r="F31" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="G31" t="s">
+      <c r="G31" s="5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B32" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C32" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D32" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E32" t="s">
+      <c r="E32" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F32" t="s">
+      <c r="F32" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="G32" t="s">
+      <c r="G32" s="5" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B33" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C33" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D33" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="E33" t="s">
+      <c r="E33" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="F33" t="s">
+      <c r="F33" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G33" t="s">
+      <c r="G33" s="5" t="s">
         <v>41</v>
       </c>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E36" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" s="5"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" s="5"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" s="5"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3CE2982-38CA-4390-8009-578A57AC8822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC4433D-F184-4E67-9B2F-E36EBB94D37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="117">
   <si>
     <t>Part Number</t>
   </si>
@@ -82,9 +82,6 @@
     <t>SOD-123</t>
   </si>
   <si>
-    <t>MBR0540 SOD-123</t>
-  </si>
-  <si>
     <t>Schottky</t>
   </si>
   <si>
@@ -100,9 +97,6 @@
     <t>КТ-93</t>
   </si>
   <si>
-    <t>2ДШ2124В94 КТ-93</t>
-  </si>
-  <si>
     <t>Schottky 1C2A</t>
   </si>
   <si>
@@ -112,9 +106,6 @@
     <t>DO-214AA</t>
   </si>
   <si>
-    <t>SS56B DO-214AA</t>
-  </si>
-  <si>
     <t>SMB</t>
   </si>
   <si>
@@ -127,9 +118,6 @@
     <t>SOD-323</t>
   </si>
   <si>
-    <t>BAT46JFILM SOD-323</t>
-  </si>
-  <si>
     <t>SOD323</t>
   </si>
   <si>
@@ -142,9 +130,6 @@
     <t>SOD-523</t>
   </si>
   <si>
-    <t>LESD5D5.0CT1G SOD-523</t>
-  </si>
-  <si>
     <t>SOD523</t>
   </si>
   <si>
@@ -154,18 +139,12 @@
     <t>SOD80C</t>
   </si>
   <si>
-    <t>BZV55-B3V3 SOD80C</t>
-  </si>
-  <si>
     <t>Nexperia</t>
   </si>
   <si>
     <t>BAS521,115</t>
   </si>
   <si>
-    <t>BAS521,115 SOD-523</t>
-  </si>
-  <si>
     <t>Diode</t>
   </si>
   <si>
@@ -175,9 +154,6 @@
     <t>TO-277A</t>
   </si>
   <si>
-    <t>V10P10-M3/86A TO-277A</t>
-  </si>
-  <si>
     <t>Vishay</t>
   </si>
   <si>
@@ -187,24 +163,15 @@
     <t>1N4148WS</t>
   </si>
   <si>
-    <t>1N4148WS SOD-323</t>
-  </si>
-  <si>
     <t>BAT54WS-E3-08</t>
   </si>
   <si>
-    <t>BAT54WS-E3-08 SOD-323</t>
-  </si>
-  <si>
     <t>LTST-C190KGKT (Green)</t>
   </si>
   <si>
     <t>0603</t>
   </si>
   <si>
-    <t>LTST-C190KGKT 0603</t>
-  </si>
-  <si>
     <t>LTST-C190KGKT</t>
   </si>
   <si>
@@ -220,18 +187,12 @@
     <t>LTST-C190KRKT (Red)</t>
   </si>
   <si>
-    <t>LTST-C190KRKT 0603</t>
-  </si>
-  <si>
     <t>LTST-C190KRKT</t>
   </si>
   <si>
     <t>LTST-C190KSKT (Yellow)</t>
   </si>
   <si>
-    <t>LTST-C190KSKT 0603</t>
-  </si>
-  <si>
     <t>LTST-C190KSKT</t>
   </si>
   <si>
@@ -241,36 +202,24 @@
     <t>SOD-923</t>
   </si>
   <si>
-    <t>ESD9L3.3ST5G SOD-923</t>
-  </si>
-  <si>
     <t>SOD923</t>
   </si>
   <si>
     <t>ESD7351HT1G</t>
   </si>
   <si>
-    <t>ESD7351HT1G SOD-323</t>
-  </si>
-  <si>
     <t>SS34</t>
   </si>
   <si>
     <t>DO-214AB</t>
   </si>
   <si>
-    <t>SS34 DO-214AB</t>
-  </si>
-  <si>
     <t>SMC</t>
   </si>
   <si>
     <t>ESD9L5.0ST5G</t>
   </si>
   <si>
-    <t>ESD9L5.0ST5G SOD-923</t>
-  </si>
-  <si>
     <t>1N5819W</t>
   </si>
   <si>
@@ -298,18 +247,12 @@
     <t>UDZSTE-175.6B</t>
   </si>
   <si>
-    <t>UDZSTE-175.6B SOD323</t>
-  </si>
-  <si>
     <t>Schottky 3C1A</t>
   </si>
   <si>
     <t>MMBZ5222BLG</t>
   </si>
   <si>
-    <t>MMBZ5222BLG SOT23</t>
-  </si>
-  <si>
     <t>SS3P6L-M3/86A</t>
   </si>
   <si>
@@ -325,9 +268,6 @@
     <t>PMEG6010CEJ</t>
   </si>
   <si>
-    <t>PMEG6010CEJ SOD323</t>
-  </si>
-  <si>
     <t>2Д663АС9</t>
   </si>
   <si>
@@ -364,9 +304,6 @@
     <t>SOD123W</t>
   </si>
   <si>
-    <t>ES07D-GS18 SOD123W</t>
-  </si>
-  <si>
     <t>Diode Array 1A2C3A</t>
   </si>
   <si>
@@ -376,18 +313,12 @@
     <t>1N5349BRLG</t>
   </si>
   <si>
-    <t>1N5349BRLG CASE 017AA</t>
-  </si>
-  <si>
     <t>1N5406</t>
   </si>
   <si>
     <t>DO-201AD</t>
   </si>
   <si>
-    <t>1N5406 DO-201AD</t>
-  </si>
-  <si>
     <t>GNL-3012GD</t>
   </si>
   <si>
@@ -409,15 +340,9 @@
     <t>SOT-23</t>
   </si>
   <si>
-    <t>1N5819W SOD123</t>
-  </si>
-  <si>
     <t>BZV55-C20V0</t>
   </si>
   <si>
-    <t>BZV55-C20V0 SOD80C</t>
-  </si>
-  <si>
     <t>BAW56W</t>
   </si>
   <si>
@@ -430,18 +355,9 @@
     <t>BZV55-C6V8</t>
   </si>
   <si>
-    <t>BZV55-C6V2 SOD80C</t>
-  </si>
-  <si>
-    <t>BZV55-C6V8 SOD80C</t>
-  </si>
-  <si>
     <t>RS3M</t>
   </si>
   <si>
-    <t>RS3M SMC</t>
-  </si>
-  <si>
     <t>DIODES</t>
   </si>
   <si>
@@ -455,6 +371,21 @@
   </si>
   <si>
     <t>LITFUSE</t>
+  </si>
+  <si>
+    <t>KA-3528EC</t>
+  </si>
+  <si>
+    <t>Kingbright</t>
+  </si>
+  <si>
+    <t>LED: 3528</t>
+  </si>
+  <si>
+    <t>HL-A-3528H343W- S1-13HL-HR3</t>
+  </si>
+  <si>
+    <t>HongLi</t>
   </si>
 </sst>
 </file>
@@ -898,103 +829,103 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" si="0"/>
         <v>BAT54A SOT-23</v>
       </c>
       <c r="D3" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="E3" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F3" t="s">
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="B4" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="C4" t="str">
         <f t="shared" si="0"/>
         <v>2Д663АС9 TO-252-2</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>110</v>
+        <v>89</v>
       </c>
       <c r="F4" t="s">
-        <v>98</v>
+        <v>78</v>
       </c>
       <c r="H4" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
         <v>100</v>
       </c>
-      <c r="B5" t="s">
-        <v>123</v>
-      </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
         <v>2Д706АС9 SOT-23</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F5" t="s">
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C6" t="str">
         <f t="shared" si="0"/>
         <v>2Д707АС9 SOT-23</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
@@ -1004,21 +935,21 @@
         <v>BAW56W SOT23</v>
       </c>
       <c r="D7" t="s">
-        <v>127</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s">
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
@@ -1028,40 +959,40 @@
         <v>BAV99 SOT23</v>
       </c>
       <c r="D8" t="s">
-        <v>128</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="B9" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="C9" t="str">
         <f>_xlfn.CONCAT(D9, " ", B9)</f>
         <v>SP4065-08ATG 10-MSOP</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="E9" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="F9" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="G9" t="s">
-        <v>139</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1078,10 +1009,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E834B2D-3CFC-49B2-A2B4-67F2231F306F}">
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="20.85546875" customWidth="1"/>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="20.85546875" customWidth="1"/>
     <col min="3" max="3" width="25.85546875" customWidth="1"/>
     <col min="4" max="8" width="20.85546875" customWidth="1"/>
   </cols>
@@ -1119,198 +1051,207 @@
       <c r="B2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
-        <v>15</v>
+      <c r="C2" t="str">
+        <f t="shared" ref="C2:C36" si="0">_xlfn.CONCAT(D2, " ", B2)</f>
+        <v>MBR0540 SOD-123</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
       <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="str">
+        <f t="shared" si="0"/>
+        <v>2ДШ2124В94 КТ-93</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>SS56B DO-214AA</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" si="0"/>
+        <v>BAT46JFILM SOD-323</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>LESD5D5.0CT1G SOD-523</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
+        <v>33</v>
+      </c>
+      <c r="C7" t="str">
+        <f t="shared" si="0"/>
+        <v>BZV55-B3V3 SOD80C</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="str">
+        <f t="shared" si="0"/>
+        <v>BAS521,115 SOD-523</v>
+      </c>
+      <c r="D8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E8" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" t="s">
-        <v>46</v>
+        <v>38</v>
+      </c>
+      <c r="C9" t="str">
+        <f t="shared" si="0"/>
+        <v>V10P10-M3/86A TO-277A</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
+        <v>26</v>
+      </c>
+      <c r="C10" t="str">
+        <f t="shared" si="0"/>
+        <v>1N4148WS SOD-323</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F10" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>12</v>
@@ -1318,114 +1259,119 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>52</v>
+        <v>26</v>
+      </c>
+      <c r="C11" t="str">
+        <f t="shared" si="0"/>
+        <v>BAT54WS-E3-08 SOD-323</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="E11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F11" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C12" t="s">
-        <v>55</v>
+        <v>44</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="0"/>
+        <v>LTST-C190KGKT 0603</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F12" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G12" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C13" t="s">
-        <v>61</v>
+        <v>44</v>
+      </c>
+      <c r="C13" t="str">
+        <f t="shared" si="0"/>
+        <v>LTST-C190KRKT 0603</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" t="s">
-        <v>64</v>
+        <v>44</v>
+      </c>
+      <c r="C14" t="str">
+        <f t="shared" si="0"/>
+        <v>LTST-C190KSKT 0603</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="G14" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
+        <v>54</v>
+      </c>
+      <c r="C15" t="str">
+        <f t="shared" si="0"/>
+        <v>ESD9L3.3ST5G SOD-923</v>
       </c>
       <c r="D15" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F15" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>12</v>
@@ -1433,22 +1379,23 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" t="s">
-        <v>71</v>
+        <v>26</v>
+      </c>
+      <c r="C16" t="str">
+        <f t="shared" si="0"/>
+        <v>ESD7351HT1G SOD-323</v>
       </c>
       <c r="D16" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>12</v>
@@ -1456,22 +1403,23 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>74</v>
+        <v>58</v>
+      </c>
+      <c r="C17" t="str">
+        <f t="shared" si="0"/>
+        <v>SS34 DO-214AB</v>
       </c>
       <c r="D17" t="s">
-        <v>72</v>
+        <v>57</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>12</v>
@@ -1479,22 +1427,23 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" t="s">
-        <v>77</v>
+        <v>54</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>ESD9L5.0ST5G SOD-923</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="E18" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F18" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>12</v>
@@ -1502,111 +1451,113 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>1N5819W SOD123</v>
+      </c>
+      <c r="D19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="C19" t="s">
-        <v>124</v>
-      </c>
-      <c r="D19" t="s">
-        <v>78</v>
-      </c>
-      <c r="E19" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
-      </c>
-      <c r="B20" t="s">
-        <v>83</v>
-      </c>
-      <c r="C20" t="s">
-        <v>83</v>
+        <v>66</v>
+      </c>
+      <c r="C20" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">GNL-3014UBD-TL </v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F20" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
+        <v>27</v>
+      </c>
+      <c r="C21" t="str">
+        <f t="shared" si="0"/>
+        <v>UDZSTE-175.6B SOD323</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E21" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F21" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
-        <v>31</v>
-      </c>
-      <c r="C22" t="s">
-        <v>87</v>
+        <v>27</v>
+      </c>
+      <c r="C22" t="str">
+        <f t="shared" si="0"/>
+        <v>UDZSTE-175.6B SOD323</v>
       </c>
       <c r="D22" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="E22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F22" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
       </c>
-      <c r="C23" t="s">
-        <v>90</v>
+      <c r="C23" t="str">
+        <f t="shared" si="0"/>
+        <v>MMBZ5222BLG SOT23</v>
       </c>
       <c r="D23" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="E23" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
@@ -1617,111 +1568,116 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>91</v>
+        <v>74</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>SS3P6L-M3/86A SS3P6L</v>
       </c>
       <c r="D24" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="F24" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
+        <v>27</v>
+      </c>
+      <c r="C25" t="str">
+        <f t="shared" si="0"/>
+        <v>PMEG6010CEJ SOD323</v>
       </c>
       <c r="D25" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="E25" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F25" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" t="s">
-        <v>102</v>
+        <v>82</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">2C117Б </v>
       </c>
       <c r="D26" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="E26" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F26" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="H26" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27" t="s">
-        <v>109</v>
+        <v>88</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="0"/>
+        <v>ES07D-GS18 SOD123W</v>
       </c>
       <c r="D27" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F27" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
-      </c>
-      <c r="C28" t="s">
-        <v>113</v>
+        <v>90</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>1N5349BRLG CASE 017AA</v>
       </c>
       <c r="D28" t="s">
-        <v>112</v>
+        <v>91</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F28" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
@@ -1729,186 +1685,242 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
+        <v>93</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="0"/>
+        <v>1N5406 DO-201AD</v>
       </c>
       <c r="D29" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F29" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
-      </c>
-      <c r="C30" t="s">
-        <v>117</v>
+        <v>99</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>GNL-3012GD GNL-3012</v>
       </c>
       <c r="D30" t="s">
-        <v>117</v>
+        <v>94</v>
       </c>
       <c r="E30" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="G30" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="B31" t="s">
-        <v>122</v>
-      </c>
-      <c r="C31" t="s">
-        <v>118</v>
+        <v>99</v>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="0"/>
+        <v>GNL-3012HD GNL-3012</v>
       </c>
       <c r="D31" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="E31" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="G31" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="B32" t="s">
-        <v>122</v>
-      </c>
-      <c r="C32" t="s">
-        <v>119</v>
+        <v>99</v>
+      </c>
+      <c r="C32" t="str">
+        <f t="shared" si="0"/>
+        <v>GNL-3012YD GNL-3012</v>
       </c>
       <c r="D32" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="E32" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="F32" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
       <c r="G32" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
-      </c>
-      <c r="C33" t="s">
-        <v>126</v>
+        <v>33</v>
+      </c>
+      <c r="C33" t="str">
+        <f t="shared" si="0"/>
+        <v>BZV55-C20V0 SOD80C</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="E33" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F33" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G33" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" t="s">
-        <v>131</v>
+        <v>33</v>
+      </c>
+      <c r="C34" t="str">
+        <f t="shared" si="0"/>
+        <v>BZV55-C6V2 SOD80C</v>
       </c>
       <c r="D34" t="s">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="E34" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F34" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G34" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="B35" t="s">
-        <v>38</v>
-      </c>
-      <c r="C35" t="s">
-        <v>132</v>
+        <v>33</v>
+      </c>
+      <c r="C35" t="str">
+        <f t="shared" si="0"/>
+        <v>BZV55-C6V8 SOD80C</v>
       </c>
       <c r="D35" t="s">
-        <v>130</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="F35" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G35" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" t="s">
-        <v>134</v>
+        <v>59</v>
+      </c>
+      <c r="C36" t="str">
+        <f t="shared" si="0"/>
+        <v>RS3M SMC</v>
       </c>
       <c r="D36" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="E36" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F36" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="G36" t="s">
-        <v>135</v>
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>112</v>
+      </c>
+      <c r="B37">
+        <v>3528</v>
+      </c>
+      <c r="C37" t="str">
+        <f>_xlfn.CONCAT(D37, " ", B37)</f>
+        <v>KA-3528EC 3528</v>
+      </c>
+      <c r="D37" t="s">
+        <v>112</v>
+      </c>
+      <c r="E37" t="s">
+        <v>46</v>
+      </c>
+      <c r="F37" t="s">
+        <v>114</v>
+      </c>
+      <c r="G37" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>115</v>
+      </c>
+      <c r="B38">
+        <v>3528</v>
+      </c>
+      <c r="C38" t="str">
+        <f>_xlfn.CONCAT(D38, " ", B38)</f>
+        <v>HL-A-3528H343W- S1-13HL-HR3 3528</v>
+      </c>
+      <c r="D38" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" t="s">
+        <v>114</v>
+      </c>
+      <c r="G38" t="s">
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAC4433D-F184-4E67-9B2F-E36EBB94D37A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B664A63-CF49-4D26-90D7-2AB5613B053B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
   <sheets>
     <sheet name="array" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="120">
   <si>
     <t>Part Number</t>
   </si>
@@ -229,9 +229,6 @@
     <t>Diode Array 1C2C3A</t>
   </si>
   <si>
-    <t>NXP</t>
-  </si>
-  <si>
     <t>LED: 3MM_G</t>
   </si>
   <si>
@@ -343,9 +340,6 @@
     <t>BZV55-C20V0</t>
   </si>
   <si>
-    <t>BAW56W</t>
-  </si>
-  <si>
     <t>BAV99</t>
   </si>
   <si>
@@ -386,6 +380,21 @@
   </si>
   <si>
     <t>HongLi</t>
+  </si>
+  <si>
+    <t>BAV99,215</t>
+  </si>
+  <si>
+    <t>Nexperia B.V.</t>
+  </si>
+  <si>
+    <t>BAW56</t>
+  </si>
+  <si>
+    <t>BAW56,215</t>
+  </si>
+  <si>
+    <t>RS3M-13-F</t>
   </si>
 </sst>
 </file>
@@ -832,7 +841,7 @@
         <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C3" t="str">
         <f t="shared" si="0"/>
@@ -848,46 +857,46 @@
         <v>11</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" t="s">
         <v>77</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="str">
+        <f t="shared" si="0"/>
+        <v>2Д663АС9 TO-252-2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F4" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" t="s">
         <v>78</v>
-      </c>
-      <c r="C4" t="str">
-        <f t="shared" si="0"/>
-        <v>2Д663АС9 TO-252-2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F4" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C5" t="str">
         <f t="shared" si="0"/>
         <v>2Д706АС9 SOT-23</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E5" t="s">
         <v>63</v>
@@ -896,46 +905,46 @@
         <v>11</v>
       </c>
       <c r="H5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>2Д707АС9 SOT-23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E6" t="s">
         <v>85</v>
-      </c>
-      <c r="B6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C6" t="str">
-        <f t="shared" si="0"/>
-        <v>2Д707АС9 SOT-23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s">
-        <v>86</v>
       </c>
       <c r="F6" t="s">
         <v>11</v>
       </c>
       <c r="H6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="B7" t="s">
         <v>11</v>
       </c>
       <c r="C7" t="str">
         <f t="shared" si="0"/>
-        <v>BAW56W SOT23</v>
+        <v>BAW56,215 SOT23</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="E7" t="s">
         <v>63</v>
@@ -944,55 +953,55 @@
         <v>11</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B8" t="s">
         <v>11</v>
       </c>
       <c r="C8" t="str">
         <f t="shared" si="0"/>
-        <v>BAV99 SOT23</v>
+        <v>BAV99,215 SOT23</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s">
         <v>11</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C9" t="str">
         <f>_xlfn.CONCAT(D9, " ", B9)</f>
         <v>SP4065-08ATG 10-MSOP</v>
       </c>
       <c r="D9" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" t="s">
         <v>108</v>
       </c>
-      <c r="E9" t="s">
-        <v>110</v>
-      </c>
       <c r="F9" t="s">
+        <v>107</v>
+      </c>
+      <c r="G9" t="s">
         <v>109</v>
-      </c>
-      <c r="G9" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -1176,7 +1185,7 @@
         <v>32</v>
       </c>
       <c r="E7" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F7" t="s">
         <v>33</v>
@@ -1475,28 +1484,28 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C20" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">GNL-3014UBD-TL </v>
       </c>
       <c r="D20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
         <v>46</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
@@ -1506,7 +1515,7 @@
         <v>UDZSTE-175.6B SOD323</v>
       </c>
       <c r="D21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -1515,12 +1524,12 @@
         <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
@@ -1530,7 +1539,7 @@
         <v>UDZSTE-175.6B SOD323</v>
       </c>
       <c r="D22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -1539,12 +1548,12 @@
         <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B23" t="s">
         <v>11</v>
@@ -1554,10 +1563,10 @@
         <v>MMBZ5222BLG SOT23</v>
       </c>
       <c r="D23" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s">
         <v>11</v>
@@ -1568,23 +1577,23 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" t="str">
+        <f t="shared" si="0"/>
+        <v>SS3P6L-M3/86A SS3P6L</v>
+      </c>
+      <c r="D24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E24" t="s">
         <v>72</v>
       </c>
-      <c r="B24" t="s">
+      <c r="F24" t="s">
         <v>74</v>
-      </c>
-      <c r="C24" t="str">
-        <f t="shared" si="0"/>
-        <v>SS3P6L-M3/86A SS3P6L</v>
-      </c>
-      <c r="D24" t="s">
-        <v>72</v>
-      </c>
-      <c r="E24" t="s">
-        <v>73</v>
-      </c>
-      <c r="F24" t="s">
-        <v>75</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>39</v>
@@ -1592,7 +1601,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
@@ -1602,7 +1611,7 @@
         <v>PMEG6010CEJ SOD323</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -1616,23 +1625,23 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">2C117Б </v>
+      </c>
+      <c r="D26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" t="s">
         <v>82</v>
       </c>
-      <c r="C26" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">2C117Б </v>
-      </c>
-      <c r="D26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
+        <v>81</v>
+      </c>
+      <c r="H26" t="s">
         <v>83</v>
-      </c>
-      <c r="F26" t="s">
-        <v>82</v>
-      </c>
-      <c r="H26" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1640,7 +1649,7 @@
         <v>40</v>
       </c>
       <c r="B27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -1653,7 +1662,7 @@
         <v>36</v>
       </c>
       <c r="F27" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G27" t="s">
         <v>39</v>
@@ -1661,23 +1670,23 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>1N5349BRLG CASE 017AA</v>
+      </c>
+      <c r="D28" t="s">
         <v>90</v>
       </c>
-      <c r="C28" t="str">
-        <f t="shared" si="0"/>
-        <v>1N5349BRLG CASE 017AA</v>
-      </c>
-      <c r="D28" t="s">
-        <v>91</v>
-      </c>
       <c r="E28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F28" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G28" t="s">
         <v>12</v>
@@ -1685,23 +1694,23 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>91</v>
+      </c>
+      <c r="B29" t="s">
         <v>92</v>
       </c>
-      <c r="B29" t="s">
-        <v>93</v>
-      </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
         <v>1N5406 DO-201AD</v>
       </c>
       <c r="D29" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E29" t="s">
         <v>36</v>
       </c>
       <c r="F29" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G29" t="s">
         <v>39</v>
@@ -1709,79 +1718,79 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B30" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
         <v>GNL-3012GD GNL-3012</v>
       </c>
       <c r="D30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E30" t="s">
         <v>46</v>
       </c>
       <c r="F30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B31" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
         <v>GNL-3012HD GNL-3012</v>
       </c>
       <c r="D31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E31" t="s">
         <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G31" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B32" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
         <v>GNL-3012YD GNL-3012</v>
       </c>
       <c r="D32" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
         <v>46</v>
       </c>
       <c r="F32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G32" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B33" t="s">
         <v>33</v>
@@ -1791,10 +1800,10 @@
         <v>BZV55-C20V0 SOD80C</v>
       </c>
       <c r="D33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E33" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F33" t="s">
         <v>33</v>
@@ -1805,7 +1814,7 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
         <v>33</v>
@@ -1815,10 +1824,10 @@
         <v>BZV55-C6V2 SOD80C</v>
       </c>
       <c r="D34" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E34" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F34" t="s">
         <v>33</v>
@@ -1829,7 +1838,7 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
         <v>33</v>
@@ -1839,10 +1848,10 @@
         <v>BZV55-C6V8 SOD80C</v>
       </c>
       <c r="D35" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E35" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F35" t="s">
         <v>33</v>
@@ -1853,17 +1862,17 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
         <v>59</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
-        <v>RS3M SMC</v>
+        <v>RS3M-13-F SMC</v>
       </c>
       <c r="D36" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="E36" t="s">
         <v>36</v>
@@ -1872,12 +1881,12 @@
         <v>59</v>
       </c>
       <c r="G36" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B37">
         <v>3528</v>
@@ -1887,21 +1896,21 @@
         <v>KA-3528EC 3528</v>
       </c>
       <c r="D37" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E37" t="s">
         <v>46</v>
       </c>
       <c r="F37" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G37" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B38">
         <v>3528</v>
@@ -1911,16 +1920,16 @@
         <v>HL-A-3528H343W- S1-13HL-HR3 3528</v>
       </c>
       <c r="D38" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E38" t="s">
         <v>46</v>
       </c>
       <c r="F38" t="s">
+        <v>112</v>
+      </c>
+      <c r="G38" t="s">
         <v>114</v>
-      </c>
-      <c r="G38" t="s">
-        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/library/diode.xlsx
+++ b/library/diode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitProjects\elem_altium_db2\library\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B664A63-CF49-4D26-90D7-2AB5613B053B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13B110CF-5B64-47AC-AA04-F0CEC552FB54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{EE2E7F00-6B54-4C0B-98D7-835E87062BAF}"/>
   </bookViews>
@@ -1061,7 +1061,7 @@
         <v>14</v>
       </c>
       <c r="C2" t="str">
-        <f t="shared" ref="C2:C36" si="0">_xlfn.CONCAT(D2, " ", B2)</f>
+        <f>_xlfn.CONCAT(D2, " ", B2)</f>
         <v>MBR0540 SOD-123</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -1085,7 +1085,7 @@
         <v>19</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D3, " ", B3)</f>
         <v>2ДШ2124В94 КТ-93</v>
       </c>
       <c r="D3" t="s">
@@ -1106,7 +1106,7 @@
         <v>22</v>
       </c>
       <c r="C4" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D4, " ", B4)</f>
         <v>SS56B DO-214AA</v>
       </c>
       <c r="D4" t="s">
@@ -1130,7 +1130,7 @@
         <v>26</v>
       </c>
       <c r="C5" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D5, " ", B5)</f>
         <v>BAT46JFILM SOD-323</v>
       </c>
       <c r="D5" t="s">
@@ -1154,7 +1154,7 @@
         <v>30</v>
       </c>
       <c r="C6" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D6, " ", B6)</f>
         <v>LESD5D5.0CT1G SOD-523</v>
       </c>
       <c r="D6" t="s">
@@ -1178,7 +1178,7 @@
         <v>33</v>
       </c>
       <c r="C7" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D7, " ", B7)</f>
         <v>BZV55-B3V3 SOD80C</v>
       </c>
       <c r="D7" t="s">
@@ -1202,7 +1202,7 @@
         <v>30</v>
       </c>
       <c r="C8" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D8, " ", B8)</f>
         <v>BAS521,115 SOD-523</v>
       </c>
       <c r="D8" t="s">
@@ -1226,7 +1226,7 @@
         <v>38</v>
       </c>
       <c r="C9" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D9, " ", B9)</f>
         <v>V10P10-M3/86A TO-277A</v>
       </c>
       <c r="D9" t="s">
@@ -1250,7 +1250,7 @@
         <v>26</v>
       </c>
       <c r="C10" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D10, " ", B10)</f>
         <v>1N4148WS SOD-323</v>
       </c>
       <c r="D10" t="s">
@@ -1274,7 +1274,7 @@
         <v>26</v>
       </c>
       <c r="C11" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D11, " ", B11)</f>
         <v>BAT54WS-E3-08 SOD-323</v>
       </c>
       <c r="D11" s="2" t="s">
@@ -1298,7 +1298,7 @@
         <v>44</v>
       </c>
       <c r="C12" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D12, " ", B12)</f>
         <v>LTST-C190KGKT 0603</v>
       </c>
       <c r="D12" t="s">
@@ -1322,7 +1322,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D13, " ", B13)</f>
         <v>LTST-C190KRKT 0603</v>
       </c>
       <c r="D13" t="s">
@@ -1346,7 +1346,7 @@
         <v>44</v>
       </c>
       <c r="C14" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D14, " ", B14)</f>
         <v>LTST-C190KSKT 0603</v>
       </c>
       <c r="D14" t="s">
@@ -1370,7 +1370,7 @@
         <v>54</v>
       </c>
       <c r="C15" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D15, " ", B15)</f>
         <v>ESD9L3.3ST5G SOD-923</v>
       </c>
       <c r="D15" t="s">
@@ -1394,7 +1394,7 @@
         <v>26</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D16, " ", B16)</f>
         <v>ESD7351HT1G SOD-323</v>
       </c>
       <c r="D16" t="s">
@@ -1418,7 +1418,7 @@
         <v>58</v>
       </c>
       <c r="C17" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D17, " ", B17)</f>
         <v>SS34 DO-214AB</v>
       </c>
       <c r="D17" t="s">
@@ -1442,7 +1442,7 @@
         <v>54</v>
       </c>
       <c r="C18" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D18, " ", B18)</f>
         <v>ESD9L5.0ST5G SOD-923</v>
       </c>
       <c r="D18" t="s">
@@ -1466,7 +1466,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D19, " ", B19)</f>
         <v>1N5819W SOD123</v>
       </c>
       <c r="D19" t="s">
@@ -1487,7 +1487,7 @@
         <v>65</v>
       </c>
       <c r="C20" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D20, " ", B20)</f>
         <v xml:space="preserve">GNL-3014UBD-TL </v>
       </c>
       <c r="D20" t="s">
@@ -1511,7 +1511,7 @@
         <v>27</v>
       </c>
       <c r="C21" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D21, " ", B21)</f>
         <v>UDZSTE-175.6B SOD323</v>
       </c>
       <c r="D21" t="s">
@@ -1535,7 +1535,7 @@
         <v>27</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D22, " ", B22)</f>
         <v>UDZSTE-175.6B SOD323</v>
       </c>
       <c r="D22" t="s">
@@ -1559,7 +1559,7 @@
         <v>11</v>
       </c>
       <c r="C23" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D23, " ", B23)</f>
         <v>MMBZ5222BLG SOT23</v>
       </c>
       <c r="D23" t="s">
@@ -1583,7 +1583,7 @@
         <v>73</v>
       </c>
       <c r="C24" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D24, " ", B24)</f>
         <v>SS3P6L-M3/86A SS3P6L</v>
       </c>
       <c r="D24" t="s">
@@ -1607,7 +1607,7 @@
         <v>27</v>
       </c>
       <c r="C25" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D25, " ", B25)</f>
         <v>PMEG6010CEJ SOD323</v>
       </c>
       <c r="D25" t="s">
@@ -1628,7 +1628,7 @@
         <v>81</v>
       </c>
       <c r="C26" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D26, " ", B26)</f>
         <v xml:space="preserve">2C117Б </v>
       </c>
       <c r="D26" t="s">
@@ -1652,7 +1652,7 @@
         <v>87</v>
       </c>
       <c r="C27" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D27, " ", B27)</f>
         <v>ES07D-GS18 SOD123W</v>
       </c>
       <c r="D27" t="s">
@@ -1676,7 +1676,7 @@
         <v>89</v>
       </c>
       <c r="C28" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D28, " ", B28)</f>
         <v>1N5349BRLG CASE 017AA</v>
       </c>
       <c r="D28" t="s">
@@ -1700,7 +1700,7 @@
         <v>92</v>
       </c>
       <c r="C29" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D29, " ", B29)</f>
         <v>1N5406 DO-201AD</v>
       </c>
       <c r="D29" t="s">
@@ -1724,7 +1724,7 @@
         <v>98</v>
       </c>
       <c r="C30" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D30, " ", B30)</f>
         <v>GNL-3012GD GNL-3012</v>
       </c>
       <c r="D30" t="s">
@@ -1748,7 +1748,7 @@
         <v>98</v>
       </c>
       <c r="C31" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D31, " ", B31)</f>
         <v>GNL-3012HD GNL-3012</v>
       </c>
       <c r="D31" t="s">
@@ -1772,7 +1772,7 @@
         <v>98</v>
       </c>
       <c r="C32" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D32, " ", B32)</f>
         <v>GNL-3012YD GNL-3012</v>
       </c>
       <c r="D32" t="s">
@@ -1796,7 +1796,7 @@
         <v>33</v>
       </c>
       <c r="C33" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D33, " ", B33)</f>
         <v>BZV55-C20V0 SOD80C</v>
       </c>
       <c r="D33" t="s">
@@ -1820,7 +1820,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D34, " ", B34)</f>
         <v>BZV55-C6V2 SOD80C</v>
       </c>
       <c r="D34" t="s">
@@ -1844,7 +1844,7 @@
         <v>33</v>
       </c>
       <c r="C35" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D35, " ", B35)</f>
         <v>BZV55-C6V8 SOD80C</v>
       </c>
       <c r="D35" t="s">
@@ -1868,7 +1868,7 @@
         <v>59</v>
       </c>
       <c r="C36" t="str">
-        <f t="shared" si="0"/>
+        <f>_xlfn.CONCAT(D36, " ", B36)</f>
         <v>RS3M-13-F SMC</v>
       </c>
       <c r="D36" t="s">
